--- a/AAII_Financials/Quarterly/ROST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ROST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
   <si>
     <t>ROST</t>
   </si>
@@ -656,514 +656,538 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43771</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43680</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43589</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43498</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43407</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43316</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43134</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6264900</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6010500</v>
+      </c>
+      <c r="F8" s="3">
         <v>6635500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>5600900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>5529200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4985000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5912300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5071400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5287500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4858100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6022500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4924800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4934900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4494700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5214200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4565500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4583000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>4333100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5020600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>4574500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4805000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>4516100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4249700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3754500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2684700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1842700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4413400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3849100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>3979900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>3796600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4107400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>3549600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>3737900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>3588600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>4067800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>3328900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>3431600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>3306400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>3510200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AQ8" s="3">
         <v>3086700</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4035800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4230600</v>
+      </c>
+      <c r="F9" s="3">
         <v>4733100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3685700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3669100</v>
       </c>
-      <c r="G9" s="3">
-        <v>3254700</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>3581400</v>
+      </c>
+      <c r="J9" s="3">
         <v>4239100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>3316600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3477200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3180500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3395600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3564300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3569400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3292600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3926200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3424000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>3399500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3196400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3773600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3326000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>3410900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3198400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>3157000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2711400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2080100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1890000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>3224200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>2766400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>2843900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>2701700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>2989700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>2547300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>2667000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>2522200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>2922600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>2369100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>2420900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>2330000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>2539600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AQ9" s="3">
         <v>2206100</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2229100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1779900</v>
+      </c>
+      <c r="F10" s="3">
         <v>1902400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1915200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1860000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1730300</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>1403600</v>
+      </c>
+      <c r="J10" s="3">
         <v>1673200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>1754700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1810300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1677600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2626900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1360600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1365500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1202100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1288000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1141500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1183500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1136700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1247000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1248500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1394100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1317700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1092700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1043100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>604600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-47300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1189200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1082700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>1136100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>1094900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1117700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>1002300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>1070900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>1066400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>1145200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>959800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>1010700</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>976400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>970600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AQ10" s="3">
         <v>880600</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1205,8 +1229,10 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1350,14 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1443,13 +1475,19 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-253000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1484,17 +1522,17 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1508,18 +1546,18 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>240000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1529,11 +1567,11 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1562,53 +1600,59 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>140200</v>
+      </c>
+      <c r="E15" s="3">
+        <v>132600</v>
+      </c>
+      <c r="F15" s="3">
         <v>134900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>132200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>126400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>115900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>117200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>111800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>108600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>109200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>119100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>102400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>98500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>99400</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1681,8 +1725,14 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1721,246 +1771,260 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5414300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5206500</v>
+      </c>
+      <c r="F17" s="3">
         <v>5821400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4952400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4890900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4378500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5181300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4467100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4628300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4267000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5278400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4374700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4377300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4038800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4655500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4117400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4066600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3865900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>4529500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>4051800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>4128700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3873400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>3847700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>3589300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2599600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2305300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>3826100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3371000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>3435800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>3259900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>3565700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>3108900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>3221600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>3046600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>3475900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>2886400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>2919200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>2804800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>3033400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AQ17" s="3">
         <v>2696300</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>850600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>804000</v>
+      </c>
+      <c r="F18" s="3">
         <v>814100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>648500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>638300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>606500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>731000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>604200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>659200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>591100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>744100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>550100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>557600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>455900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>558700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>448100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>516400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>467200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>491100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>522700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>676300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>642700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>402000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>165200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>85100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-462600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>587300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>478100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>544100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>536700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>541700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>440700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>516300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>542000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>591900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>442500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>512400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>501600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>476800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AQ18" s="3">
         <v>390400</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2002,8 +2066,10 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2043,26 +2109,26 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>43100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>23700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>9700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>200</v>
       </c>
       <c r="W20" s="3">
         <v>200</v>
@@ -2071,534 +2137,564 @@
         <v>200</v>
       </c>
       <c r="Y20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>5500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>6700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>7100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>8500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>8800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>7100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>5700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>4200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>2900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>2400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>1700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>1100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AQ20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>990800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>936600</v>
+      </c>
+      <c r="F21" s="3">
         <v>949000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>780700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>764700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>722400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>848200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>716000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>767800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>700300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>863100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>652600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>656200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>555200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>705900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>573200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>623200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>560500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>589900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>611000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>763100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>730400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>498300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>254100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>174900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-368700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>688600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>573000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>635400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>627900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>634700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>531600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>604600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>626700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>682000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>521700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>589900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>579100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>556300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AQ21" s="3">
         <v>466600</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F22" s="3">
         <v>8500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>9000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>8000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>12500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>13800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>15400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>16900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>17300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>17700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>18200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>18700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>19400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>20400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>20900</v>
       </c>
       <c r="R22" s="3">
         <v>20400</v>
       </c>
       <c r="S22" s="3">
-        <v>18900</v>
+        <v>20900</v>
       </c>
       <c r="T22" s="3">
-        <v>18000</v>
+        <v>20400</v>
       </c>
       <c r="U22" s="3">
         <v>18900</v>
       </c>
       <c r="V22" s="3">
+        <v>18000</v>
+      </c>
+      <c r="W22" s="3">
         <v>18900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
+        <v>18900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>19300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>19400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>29100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>29600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>10000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>2200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>2300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>2400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>2800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>3500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>4200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>4200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>4600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>4700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>4800</v>
-      </c>
-      <c r="AM22" s="3">
-        <v>4900</v>
-      </c>
-      <c r="AN22" s="3">
-        <v>4900</v>
       </c>
       <c r="AO22" s="3">
         <v>4900</v>
       </c>
+      <c r="AP22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>4900</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1134800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>837500</v>
+      </c>
+      <c r="F23" s="3">
         <v>848300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>682400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>670600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>640900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>770800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>646700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>702600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>637100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>796200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>593400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>594900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>487300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>581400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>450900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>505700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>449500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>473300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>504000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>657600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>623600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>382900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>136500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>56200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-469300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>590600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>482500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>548800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>542400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>547000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>443700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>517800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>542500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>591500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>440700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>510000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>498500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>473000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AQ23" s="3">
         <v>386300</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>283500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>187500</v>
+      </c>
+      <c r="F24" s="3">
         <v>202400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>170500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>162600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>161600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>184000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>157900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>175400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>149100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>186600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>146100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>148500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>116100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>134400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>108800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>121200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>111000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>106500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>119000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>163400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>147100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>144900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>34200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-163400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>134500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>111600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>136100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>121200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>105300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>105500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>128400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>124200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>220900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>166200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>193500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>177500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>172500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AQ24" s="3">
         <v>141700</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2716,246 +2812,264 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>851300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>650000</v>
+      </c>
+      <c r="F26" s="3">
         <v>645900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>511900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>508000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>479200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>586800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>488800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>527100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>488000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>609700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>447300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>446300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>371200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>447000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>342000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>384500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>338400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>366800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>385000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>494300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>476500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>238000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>131200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>22000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-305800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>456100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>370900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>412700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>421100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>441700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>338100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>389400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>418300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>370600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>274400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>316500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>321000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>300600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AQ26" s="3">
         <v>244500</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>851300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>650000</v>
+      </c>
+      <c r="F27" s="3">
         <v>645900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>511900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>508000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>479200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>586800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>488800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>527100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>488000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>609700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>447300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>446300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>371200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>447000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>342000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>384500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>338400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>366800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>385000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>494300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>476500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>238000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>131200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>22000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-305800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>456100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>370900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>412700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>421100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>441700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>338100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>389400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>418300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>370600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>274400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>316500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>321000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>300600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AQ27" s="3">
         <v>244500</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3073,8 +3187,14 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3156,11 +3276,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3174,15 +3294,15 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>80100</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3192,8 +3312,14 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3311,8 +3437,14 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3430,8 +3562,14 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3471,26 +3609,26 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-43100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-23700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-9700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-200</v>
       </c>
       <c r="W32" s="3">
         <v>-200</v>
@@ -3499,177 +3637,189 @@
         <v>-200</v>
       </c>
       <c r="Y32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-7100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-4200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AQ32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>851300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>650000</v>
+      </c>
+      <c r="F33" s="3">
         <v>645900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>511900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>508000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>479200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>586800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>488800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>527100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>488000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>609700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>447300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>446300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>371200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>447000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>342000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>384500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>338400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>366800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>385000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>494300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>476500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>238000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>131200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>22000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-305800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>456100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>370900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>412700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>421100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>441700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>338100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>389400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>418300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>450700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>274400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>316500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>321000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>300600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AQ33" s="3">
         <v>244500</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3787,251 +3937,269 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>851300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>650000</v>
+      </c>
+      <c r="F35" s="3">
         <v>645900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>511900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>508000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>479200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>586800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>488800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>527100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>488000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>609700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>447300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>446300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>371200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>447000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>342000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>384500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>338400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>366800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>385000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>494300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>476500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>238000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>131200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>22000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-305800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>456100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>370900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>412700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>421100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>441700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>338100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>389400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>418300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>450700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>274400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>316500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>321000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>300600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AQ35" s="3">
         <v>244500</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43771</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43680</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43589</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43498</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43407</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43316</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43134</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4073,8 +4241,10 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4116,127 +4286,135 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4288100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4131000</v>
+      </c>
+      <c r="F41" s="3">
         <v>4594400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4061200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3847000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3783400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4730700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4349300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4668100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4654300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>4872400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4499500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4583600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>4416500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4551900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3906500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3903700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4015600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4922400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>5259600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5569100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>5367000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>4819300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4416100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>3793000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2669500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1351200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1142700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1382000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1366600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>1412900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>1349200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>1386900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>1302800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>1290300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>1144200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>1150900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>1244200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>1111600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AQ41" s="3">
         <v>878800</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4337,263 +4515,281 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
         <v>500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>500</v>
       </c>
-      <c r="AL42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM42" s="3">
-        <v>0</v>
-      </c>
       <c r="AN42" s="3">
         <v>0</v>
       </c>
       <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ42" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>248100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>212500</v>
+      </c>
+      <c r="F43" s="3">
         <v>194100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>203900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>210500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>181000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>156900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>176200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>181900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>165400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>142900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>171900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>175400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>170800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>145700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>168500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>167500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>164100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>119200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>158800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>159200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>167100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>115100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>122700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>162700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>49600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>102200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>124900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>130400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>121600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>96700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>117800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>121500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>109400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>87900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>103100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>103400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>100800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>75200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AQ43" s="3">
         <v>91400</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3087400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2977000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2631000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>3129000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2608500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2669800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2444500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2859100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2490600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2461700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2192200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2613800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2300100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>2241700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2023500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2494000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2716900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2673600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2262300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2231200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>1751000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>1698000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>1509000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1630400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>1118000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1757300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1832300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>2168800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1835900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1813800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>1750400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>1979100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>1698400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>1895500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>1641700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>1840200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>1608300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>1594800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>1512900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AQ44" s="3">
         <v>1763700</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4612,15 +4808,15 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>21100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4633,205 +4829,217 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>183700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>192200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>197000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>194800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>169300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>195300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>193600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>199400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>249100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>347400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>273600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>111500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>147000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>170300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>167600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>160700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>144000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>177200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>172800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>146400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>130700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>148000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>141800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>124900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>113400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AQ45" s="3">
         <v>140700</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7876400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7573400</v>
+      </c>
+      <c r="F46" s="3">
         <v>7640100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7629700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>6925800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6875100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7538700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7626300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7595000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7507400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7398100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>7491900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>7273800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>7039600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6904700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6761200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>6985100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>7048000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>7473200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>7844900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>7672800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>7431500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>6692500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>6516600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5347400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>4587900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3432800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3606700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>3515900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>3462700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>3404000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>3623300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>3379700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>3454100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>3151200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>3235900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>3004400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>3064700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>2813000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AQ46" s="3">
         <v>2875400</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4871,11 +5079,11 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4916,20 +5124,20 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
+      <c r="AE47" s="3">
+        <v>0</v>
       </c>
       <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3">
         <v>100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>500</v>
-      </c>
-      <c r="AH47" s="3">
-        <v>700</v>
-      </c>
-      <c r="AI47" s="3">
-        <v>700</v>
       </c>
       <c r="AJ47" s="3">
         <v>700</v>
@@ -4938,10 +5146,10 @@
         <v>700</v>
       </c>
       <c r="AL47" s="3">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="AM47" s="3">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="AN47" s="3">
         <v>1300</v>
@@ -4949,127 +5157,139 @@
       <c r="AO47" s="3">
         <v>1300</v>
       </c>
+      <c r="AP47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AQ47" s="3">
+        <v>1300</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7803200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7679600</v>
+      </c>
+      <c r="F48" s="3">
         <v>7608400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7485300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7280900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7153400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7087300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7007100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6817700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6725600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>6658700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6557500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6475300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>6347200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>6279700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6110600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>5955600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>5945600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5925800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5816500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5720100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5718600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5795300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>5838900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5759800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>5775100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>5707200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>5608200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>5437200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>5379400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>2475200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>2418200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>2384300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>2369200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>2382500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>2348200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>2327100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>2308700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>2328000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AQ48" s="3">
         <v>2310700</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5187,8 +5407,14 @@
       <c r="AO49" s="3">
         <v>0</v>
       </c>
+      <c r="AP49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5306,8 +5532,14 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5425,127 +5657,139 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>302800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>301500</v>
+      </c>
+      <c r="F52" s="3">
         <v>300300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>300000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>288800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>276100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>279400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>271800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>265300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>258800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>243200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>221100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>238300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>232100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>232100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>228300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>239300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>240100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>241300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>254400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>248400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>245700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>230100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>215200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>215000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>365000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>208300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>201000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>198800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>207100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>194300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>193800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>199100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>196800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>187700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>182100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>181700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>178300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>167000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AQ52" s="3">
         <v>162500</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5663,127 +5907,139 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15982300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>15554600</v>
+      </c>
+      <c r="F54" s="3">
         <v>15548700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>15415000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14495500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>14304600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14905300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>14905200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>14678000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>14491800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>14300100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>14270600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>13987300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13618900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>13416500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>13100100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>13179900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>13233700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>13640300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>13915700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>13641400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>13395900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>12717900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>12570700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>11322200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>10728000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>9348400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>9415800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>9151900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>9049100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>6073700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>6235800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>5963800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>6020800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>5722100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>5767000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>5514500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>5553000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>5309400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AQ54" s="3">
         <v>5349900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5825,8 +6081,10 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5868,172 +6126,180 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2621700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2653700</v>
+      </c>
+      <c r="F57" s="3">
         <v>2386400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2645200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2205600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2164000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2126300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2346500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>2217200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2119100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1955900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2280300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>2151000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>2061500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2009900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1927800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>2085700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>2175400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>2372300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2652900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>2588600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>2574800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>2256900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2426400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1009700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>706300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1296500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1480200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1359800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>1296200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1177100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>1394000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>1184400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>1299100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>1059800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>1289600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>1172800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>1178000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>1021700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AQ57" s="3">
         <v>1149100</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>993800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>976900</v>
+      </c>
+      <c r="F58" s="3">
         <v>1227600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1222900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1215300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1200800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1403100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1398600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1640100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1628200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>933300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>929700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>668000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>654700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6044,34 +6310,34 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>65000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>65000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>64900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>64900</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB58" s="3">
         <v>802500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>805000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -6080,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="AG58" s="3">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="AH58" s="3">
-        <v>85000</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3">
         <v>85000</v>
@@ -6091,11 +6357,11 @@
       <c r="AJ58" s="3">
         <v>85000</v>
       </c>
-      <c r="AK58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL58" s="3" t="s">
-        <v>8</v>
+      <c r="AK58" s="3">
+        <v>85000</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>85000</v>
       </c>
       <c r="AM58" s="3" t="s">
         <v>8</v>
@@ -6106,484 +6372,514 @@
       <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ58" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>211000</v>
+      </c>
+      <c r="F59" s="3">
         <v>87000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>23100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>180100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>67800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>23300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>212700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>100100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>21000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>25400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>158200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1626300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1536500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1559300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1580700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>1842600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1758400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>1682700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1678700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>1645200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1515200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>1340900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1112400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1405500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1378000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>1319600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1297300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>832400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>773300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>708700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>722500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>781600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>766600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>656100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>759700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>730800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AQ59" s="3">
         <v>738800</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4885500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4914900</v>
+      </c>
+      <c r="F60" s="3">
         <v>4827200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5019800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>4392000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4435800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4661800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>4843700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4874200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>4885500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>4185800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>4405700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3969600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3781200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3636200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3464200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>3645000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>3756100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>4214900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>4476300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>4336200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>4318400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>3967000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>3941600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>3153100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2623600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2701900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2858200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2679400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2593500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2009500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>2252300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>1978100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>2106600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>1926400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>2056200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>1829000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>1937700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>1752500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AQ60" s="3">
         <v>1887900</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3745400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3746300</v>
+      </c>
+      <c r="F61" s="3">
         <v>3984700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3965600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3852700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3814800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4279400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4335900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4224100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4206500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4814400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4850100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>5112200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>5077000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2456500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>2455500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2454400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2453400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2452300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2451300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2450200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>2449200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2448200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2512000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2286300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2285600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>312900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>312800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>312700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>312600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>312400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>312300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>312200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>312100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>312000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>396800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>396700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>396600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>396500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AQ61" s="3">
         <v>396400</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>295600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>292900</v>
+      </c>
+      <c r="F62" s="3">
         <v>287900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>295300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>279300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>268700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>267900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>265700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>254500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>245100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>232400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>219000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>231900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>222500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3035100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3033400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2953600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2970400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2913000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3004900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2951000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2975400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3012000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3098000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3015700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3001400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2974300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2968000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>2863600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>2875500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>446000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>484000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>488800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>471800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>434300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>455400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>448900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>440900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>412300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AQ62" s="3">
         <v>416000</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6701,8 +6997,14 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6820,8 +7122,14 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6939,127 +7247,139 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9239100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9249600</v>
+      </c>
+      <c r="F66" s="3">
         <v>9361300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9531000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>8763000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>8728500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9396100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9641800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9547500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>9543800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9428800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>9687700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>9532600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9308500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>9127900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>8953100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>9053000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>9179800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>9580200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9932500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>9737400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>9743000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>9427200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>9551600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8455000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>7910700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>5989100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>6139100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>5855700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>5781600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2767900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>3048600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>2779100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>2890500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>2672700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>2908500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>2674600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>2775200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>2561300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AQ66" s="3">
         <v>2700400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7101,8 +7421,10 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7220,8 +7542,14 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7339,8 +7667,14 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7458,8 +7792,14 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7577,127 +7917,139 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5316400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4921000</v>
+      </c>
+      <c r="F72" s="3">
         <v>4726200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4467800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4342400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4220800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4128200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3918700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3807400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3658500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3548700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3292000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3189100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3079500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3049700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2931600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>2928600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2875200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2874900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2833500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2782900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2560600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2185800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1947800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1816600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1794600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2330700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2267100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>2304700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2295900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>2298800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>2200700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>2216900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>2176900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>2071400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1900900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>1898200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>1850500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>1801100</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AQ72" s="3">
         <v>1717900</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7815,8 +8167,14 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7934,8 +8292,14 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8053,127 +8417,139 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6743200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6305000</v>
+      </c>
+      <c r="F76" s="3">
         <v>6187400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5884000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5732600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5576100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5509200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5263400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5130500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4948000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4871300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4583000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4454700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4310400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4288600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4147000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4127000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4053900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4060100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3983200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3904000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3652800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3290600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>3019000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>2867200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2817400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>3359200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3276800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>3296300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>3267500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>3305700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>3187200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>3184600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>3130300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>3049300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>2858500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>2839900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>2777700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>2748000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AQ76" s="3">
         <v>2649500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8291,251 +8667,269 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43771</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43680</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43589</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43498</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43407</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43316</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43225</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43134</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>851300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>650000</v>
+      </c>
+      <c r="F81" s="3">
         <v>645900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>511900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>508000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>479200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>586800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>488800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>527100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>488000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>609700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>447300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>446300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>371200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>447000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>342000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>384500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>338400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>366800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>385000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>494300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>476500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>238000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>131200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>22000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-305800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>456100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>370900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>412700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>421100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>441700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>338100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>389400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>418300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>450700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>274400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>316500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>321000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>300600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AQ81" s="3">
         <v>244500</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8577,127 +8971,135 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>126400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>115900</v>
+      </c>
+      <c r="F83" s="3">
         <v>117200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>111800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>108600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>109200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>119100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>102400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>98500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>99400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>104100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>101400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>97100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>92100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>104100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>101400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>97100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>92100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>98500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>88000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>86600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>87500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>96100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>88600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>89000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>90600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>95800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>88200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>84100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>82800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>84200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>83700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>82600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>79800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>85900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>76400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>75100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>75800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>78400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AQ83" s="3">
         <v>75500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8815,8 +9217,14 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8934,8 +9342,14 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9053,8 +9467,14 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9172,8 +9592,14 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9291,127 +9717,139 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>875800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>836000</v>
+      </c>
+      <c r="F89" s="3">
         <v>1121700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>827100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>668400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>409700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>882600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>513400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>592100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>368900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>948800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>449500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>703100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>413200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1216700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>528900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>360000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-416300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>235200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>158300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>592600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>752800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>462800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1610700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1230900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-1058400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>760600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>327500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>574500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>509000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>616600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>435900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>542100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>472100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>515600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>367700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>277100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>520900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>529600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AQ89" s="3">
         <v>249700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9453,127 +9891,135 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-251300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-209000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-209300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-201700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-207400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-206000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-180400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-197500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-136200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-222400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-177000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-196200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-167300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-236200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-174600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-133500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-109800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-179900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-123500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-117500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-136900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-65900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-89500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-110300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-139700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-154200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-150900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-154700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-95600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-120500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-114700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-98800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-79800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-104600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-97500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-93300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-76000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-77400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AQ91" s="3">
         <v>-73000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9691,8 +10137,14 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9810,127 +10262,139 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-251300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-209000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-209300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-201700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-207400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-123300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-180400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-197500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-136200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-222400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-177000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-196200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-167300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-236200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-174600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-133500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-109800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-179900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-123500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-117500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-136900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-65900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-89500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-110300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-139700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-154200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-150900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-154700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-95100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-117800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-114500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-98800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-79300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-87100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-96700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-93300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-76000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-76700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AQ94" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9972,127 +10436,135 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>142600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>143600</v>
+      </c>
+      <c r="F96" s="3">
         <v>130900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>131600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>132300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>133300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>121200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>121700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>122500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>123300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>112700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>113300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>114000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>114800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-106600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-107500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-108300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-108900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-100600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-101100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-101900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-101500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-101400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-91400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-91700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-92900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-93700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-83300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AI96" s="3">
         <v>-83900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AJ96" s="3">
         <v>-84600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AK96" s="3">
         <v>-85400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AL96" s="3">
         <v>-61100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AM96" s="3">
         <v>-61500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AN96" s="3">
         <v>-62200</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AO96" s="3">
         <v>-62800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>-53100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AQ96" s="3">
         <v>-53500</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10210,8 +10682,14 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10329,8 +10807,14 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10448,127 +10932,139 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-466700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1089900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-387000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-403000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-402300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1149800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-377400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-651100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-380000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-450000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-353000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-355700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-339100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-380600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-335000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-351500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-338300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-380700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-392400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-344300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-272800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-142800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>5000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-823300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>3000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>2517100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-398500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-416400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-408900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-459400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-432300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-359300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-358900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-380900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-282400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-278000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-276900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-312200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-220100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AQ100" s="3">
         <v>-229600</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10608,11 +11104,11 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10686,123 +11182,135 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-462800</v>
+      </c>
+      <c r="F102" s="3">
         <v>533800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>214800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>64300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-947500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>381800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-318100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>14600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-217400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>373400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-83300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>167800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-134700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>645500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-111800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-906800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-337200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-309500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>202300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>473000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>401900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>697900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1123500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1319000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>207900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-239900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>10900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-45600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>66500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-37900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>84400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>146100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-7000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>-93100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>132700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>232800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AQ102" s="3">
         <v>-48900</v>
       </c>
     </row>
